--- a/output/pdf_financials_xlsx/MMM.xlsx
+++ b/output/pdf_financials_xlsx/MMM.xlsx
@@ -909,28 +909,28 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.03939</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.09543600000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.072295</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.031401</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.058788</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.060518</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.037617</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.129588</v>
       </c>
     </row>
     <row r="13">
@@ -1652,28 +1652,28 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.297578</v>
+        <v>-3.336968</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-6.398948</v>
+        <v>-6.494384</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.682336</v>
+        <v>1.610041</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.62404</v>
+        <v>-1.655441</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.571721</v>
+        <v>-2.630509</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.403791</v>
+        <v>-1.464309</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.401486</v>
+        <v>-0.439103</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>4.692286</v>
+        <v>4.562698</v>
       </c>
     </row>
     <row r="28">
@@ -1742,28 +1742,28 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.297578</v>
+        <v>-3.336968</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.398948</v>
+        <v>-6.494384</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.682336</v>
+        <v>1.610041</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.62404</v>
+        <v>-1.655441</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.571721</v>
+        <v>-2.630509</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.403791</v>
+        <v>-1.464309</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.401486</v>
+        <v>-0.439103</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>4.692286</v>
+        <v>4.562698</v>
       </c>
     </row>
     <row r="30">
@@ -1982,7 +1982,7 @@
         <v>2.899097</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.387996</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.882238</v>
@@ -1991,10 +1991,10 @@
         <v>0.391301</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.212636</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.430956</v>
       </c>
     </row>
     <row r="35">
@@ -2072,7 +2072,7 @@
         <v>2.919097</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.02</v>
+        <v>0.407996</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.902238</v>
@@ -2081,10 +2081,10 @@
         <v>0.411301</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.72</v>
+        <v>0.932636</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.02</v>
+        <v>0.450956</v>
       </c>
     </row>
     <row r="37">
@@ -2612,7 +2612,7 @@
         <v>10.257112</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>9.66869</v>
+        <v>9.280694</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>6.045585</v>
@@ -2621,10 +2621,10 @@
         <v>5.150792</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.446925</v>
+        <v>4.234289</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>9.907933999999999</v>
+        <v>9.476978000000001</v>
       </c>
     </row>
     <row r="49">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24020,7 +24020,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -24494,7 +24494,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -28130,7 +28130,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">

--- a/output/pdf_financials_xlsx/MMM.xlsx
+++ b/output/pdf_financials_xlsx/MMM.xlsx
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.477708</v>
+        <v>0.527457</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.391562</v>
+        <v>0.44575</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.421855</v>
+        <v>0.494979</v>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
@@ -684,28 +684,28 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.171132</v>
+        <v>0.235632</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.167917</v>
+        <v>0.223417</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.072751</v>
+        <v>0.129251</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.039847</v>
+        <v>0.062847</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.044846</v>
+        <v>0.07084600000000001</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.047679</v>
+        <v>0.07367899999999999</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.042216</v>
+        <v>0.066216</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.038575</v>
+        <v>0.061575</v>
       </c>
     </row>
     <row r="8">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>1.387337</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>0</v>
@@ -5785,18 +5785,14 @@
       <c r="G119" s="3" t="n">
         <v>-0.037064</v>
       </c>
-      <c r="H119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H119" s="3" t="n">
+        <v>-0.052044</v>
       </c>
       <c r="I119" s="3" t="n">
         <v>-0.000853</v>
       </c>
-      <c r="J119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K119" s="3" t="n">
         <v>0</v>
@@ -5804,10 +5800,8 @@
       <c r="L119" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -6511,18 +6505,14 @@
       <c r="G135" s="3" t="n">
         <v>-2.208501</v>
       </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H135" s="3" t="n">
+        <v>1.522454</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-1.970424</v>
       </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J135" s="3" t="n">
+        <v>0.671812</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-0.367014</v>
@@ -6530,10 +6520,8 @@
       <c r="L135" s="3" t="n">
         <v>-0.119771</v>
       </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M135" s="3" t="n">
+        <v>0.283173</v>
       </c>
     </row>
   </sheetData>
@@ -14724,7 +14712,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -21710,7 +21702,11 @@
           <t>Net cash generated from investing activities</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -23798,7 +23794,11 @@
           <t>Net cash generated from investing activities</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E233" s="5" t="n">
         <v>5.977656</v>
       </c>
@@ -24428,7 +24428,11 @@
           <t>Directors’ fees (note 9)</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -30152,7 +30156,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -31936,7 +31944,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E344" s="5" t="n">
         <v>0.049749</v>
       </c>
